--- a/Excel/ShengxiaoGroupConfig.xlsx
+++ b/Excel/ShengxiaoGroupConfig.xlsx
@@ -27,12 +27,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="13">
   <si>
     <t>#</t>
   </si>
   <si>
     <t>_Id</t>
+  </si>
+  <si>
+    <t>Cycle</t>
   </si>
   <si>
     <t>Quality</t>
@@ -1020,22 +1023,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:H21"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" outlineLevelCol="7"/>
+  <dimension ref="C1:I38"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="3" width="9" style="1"/>
-    <col min="4" max="5" width="16.25" style="1" customWidth="1"/>
-    <col min="6" max="7" width="13.875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="12.25" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="1"/>
+    <col min="1" max="4" width="9" style="1"/>
+    <col min="5" max="6" width="16.25" style="1" customWidth="1"/>
+    <col min="7" max="8" width="13.875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="12.25" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="8:8">
-      <c r="H1" s="1" t="s">
+    <row r="1" spans="3:9">
+      <c r="I1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" ht="13.5" spans="3:7">
+    <row r="3" ht="13.5" spans="3:9">
       <c r="C3" s="2" t="s">
         <v>1</v>
       </c>
@@ -1051,10 +1054,13 @@
       <c r="G3" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" ht="13.5" spans="3:7">
+      <c r="H3" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" ht="13.5" spans="3:9">
       <c r="C4" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>2</v>
@@ -1068,347 +1074,769 @@
       <c r="G4" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" ht="13.5" spans="3:7">
+      <c r="H4" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" ht="13.5" spans="3:9">
       <c r="C5" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="3:8">
+        <v>8</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="3:9">
       <c r="C6" s="1">
         <v>1</v>
       </c>
       <c r="D6" s="1">
+        <v>1</v>
+      </c>
+      <c r="E6" s="1">
         <v>6</v>
       </c>
-      <c r="E6" s="1">
+      <c r="F6" s="1">
         <v>3</v>
       </c>
-      <c r="F6" s="1">
+      <c r="G6" s="1">
         <v>93</v>
       </c>
-      <c r="G6" s="1">
+      <c r="H6" s="1">
         <v>5</v>
       </c>
-      <c r="H6" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="3:8">
+      <c r="I6" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="3:9">
       <c r="C7" s="1">
         <v>2</v>
       </c>
       <c r="D7" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E7" s="1">
         <v>6</v>
       </c>
       <c r="F7" s="1">
+        <v>6</v>
+      </c>
+      <c r="G7" s="1">
         <v>92</v>
       </c>
-      <c r="G7" s="1">
+      <c r="H7" s="1">
         <v>5</v>
       </c>
-      <c r="H7" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="3:8">
+      <c r="I7" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="3:9">
       <c r="C8" s="1">
         <v>3</v>
       </c>
       <c r="D8" s="1">
+        <v>1</v>
+      </c>
+      <c r="E8" s="1">
         <v>6</v>
       </c>
-      <c r="E8" s="1">
-        <v>9</v>
-      </c>
       <c r="F8" s="1">
+        <v>9</v>
+      </c>
+      <c r="G8" s="1">
         <v>91</v>
       </c>
-      <c r="G8" s="1">
+      <c r="H8" s="1">
         <v>5</v>
       </c>
-      <c r="H8" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="3:8">
+      <c r="I8" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="3:9">
       <c r="C9" s="1">
         <v>4</v>
       </c>
       <c r="D9" s="1">
+        <v>1</v>
+      </c>
+      <c r="E9" s="1">
         <v>6</v>
       </c>
-      <c r="E9" s="1">
+      <c r="F9" s="1">
         <v>12</v>
       </c>
-      <c r="F9" s="1">
+      <c r="G9" s="1">
         <v>94</v>
       </c>
-      <c r="G9" s="1">
+      <c r="H9" s="1">
         <v>5</v>
       </c>
-      <c r="H9" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="3:8">
+      <c r="I9" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="3:9">
       <c r="C10" s="1">
         <v>5</v>
       </c>
       <c r="D10" s="1">
+        <v>1</v>
+      </c>
+      <c r="E10" s="1">
         <v>7</v>
       </c>
-      <c r="E10" s="1">
+      <c r="F10" s="1">
         <v>3</v>
       </c>
-      <c r="F10" s="1">
+      <c r="G10" s="1">
         <v>93</v>
       </c>
-      <c r="G10" s="1">
+      <c r="H10" s="1">
         <v>10</v>
       </c>
-      <c r="H10" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="3:8">
+      <c r="I10" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="3:9">
       <c r="C11" s="1">
         <v>6</v>
       </c>
       <c r="D11" s="1">
+        <v>1</v>
+      </c>
+      <c r="E11" s="1">
         <v>7</v>
       </c>
-      <c r="E11" s="1">
+      <c r="F11" s="1">
         <v>6</v>
       </c>
-      <c r="F11" s="1">
+      <c r="G11" s="1">
         <v>92</v>
       </c>
-      <c r="G11" s="1">
+      <c r="H11" s="1">
         <v>10</v>
       </c>
-      <c r="H11" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="3:8">
+      <c r="I11" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="3:9">
       <c r="C12" s="1">
         <v>7</v>
       </c>
       <c r="D12" s="1">
+        <v>1</v>
+      </c>
+      <c r="E12" s="1">
         <v>7</v>
       </c>
-      <c r="E12" s="1">
-        <v>9</v>
-      </c>
       <c r="F12" s="1">
+        <v>9</v>
+      </c>
+      <c r="G12" s="1">
         <v>91</v>
       </c>
-      <c r="G12" s="1">
+      <c r="H12" s="1">
         <v>10</v>
       </c>
-      <c r="H12" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="3:8">
+      <c r="I12" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="3:9">
       <c r="C13" s="1">
         <v>8</v>
       </c>
       <c r="D13" s="1">
+        <v>1</v>
+      </c>
+      <c r="E13" s="1">
         <v>7</v>
       </c>
-      <c r="E13" s="1">
+      <c r="F13" s="1">
         <v>12</v>
       </c>
-      <c r="F13" s="1">
+      <c r="G13" s="1">
         <v>94</v>
       </c>
-      <c r="G13" s="1">
+      <c r="H13" s="1">
         <v>10</v>
       </c>
-      <c r="H13" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="3:8">
+      <c r="I13" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="3:9">
       <c r="C14" s="1">
         <v>9</v>
       </c>
       <c r="D14" s="1">
+        <v>1</v>
+      </c>
+      <c r="E14" s="1">
         <v>8</v>
       </c>
-      <c r="E14" s="1">
+      <c r="F14" s="1">
         <v>3</v>
       </c>
-      <c r="F14" s="1">
+      <c r="G14" s="1">
         <v>93</v>
       </c>
-      <c r="G14" s="1">
+      <c r="H14" s="1">
         <v>15</v>
       </c>
-      <c r="H14" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15" spans="3:8">
+      <c r="I14" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="3:9">
       <c r="C15" s="1">
         <v>10</v>
       </c>
       <c r="D15" s="1">
+        <v>1</v>
+      </c>
+      <c r="E15" s="1">
         <v>8</v>
       </c>
-      <c r="E15" s="1">
+      <c r="F15" s="1">
         <v>6</v>
       </c>
-      <c r="F15" s="1">
+      <c r="G15" s="1">
         <v>92</v>
       </c>
-      <c r="G15" s="1">
+      <c r="H15" s="1">
         <v>15</v>
       </c>
-      <c r="H15" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="16" spans="3:8">
+      <c r="I15" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="3:9">
       <c r="C16" s="1">
         <v>11</v>
       </c>
       <c r="D16" s="1">
+        <v>1</v>
+      </c>
+      <c r="E16" s="1">
         <v>8</v>
       </c>
-      <c r="E16" s="1">
-        <v>9</v>
-      </c>
       <c r="F16" s="1">
+        <v>9</v>
+      </c>
+      <c r="G16" s="1">
         <v>91</v>
       </c>
-      <c r="G16" s="1">
+      <c r="H16" s="1">
         <v>15</v>
       </c>
-      <c r="H16" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" spans="3:8">
+      <c r="I16" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="3:9">
       <c r="C17" s="1">
         <v>12</v>
       </c>
       <c r="D17" s="1">
+        <v>1</v>
+      </c>
+      <c r="E17" s="1">
         <v>8</v>
       </c>
-      <c r="E17" s="1">
+      <c r="F17" s="1">
         <v>12</v>
       </c>
-      <c r="F17" s="1">
+      <c r="G17" s="1">
         <v>94</v>
       </c>
-      <c r="G17" s="1">
+      <c r="H17" s="1">
         <v>15</v>
       </c>
-      <c r="H17" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="18" spans="3:8">
+      <c r="I17" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="3:9">
       <c r="C18" s="1">
         <v>13</v>
       </c>
       <c r="D18" s="1">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E18" s="1">
+        <v>9</v>
+      </c>
+      <c r="F18" s="1">
         <v>3</v>
       </c>
-      <c r="F18" s="1">
+      <c r="G18" s="1">
         <v>93</v>
       </c>
-      <c r="G18" s="1">
+      <c r="H18" s="1">
         <v>20</v>
       </c>
-      <c r="H18" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="19" spans="3:8">
+      <c r="I18" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="3:9">
       <c r="C19" s="1">
         <v>14</v>
       </c>
       <c r="D19" s="1">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E19" s="1">
+        <v>9</v>
+      </c>
+      <c r="F19" s="1">
         <v>6</v>
       </c>
-      <c r="F19" s="1">
+      <c r="G19" s="1">
         <v>92</v>
       </c>
-      <c r="G19" s="1">
+      <c r="H19" s="1">
         <v>20</v>
       </c>
-      <c r="H19" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="20" spans="3:8">
+      <c r="I19" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="3:9">
       <c r="C20" s="1">
         <v>15</v>
       </c>
       <c r="D20" s="1">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E20" s="1">
         <v>9</v>
       </c>
       <c r="F20" s="1">
+        <v>9</v>
+      </c>
+      <c r="G20" s="1">
         <v>91</v>
       </c>
-      <c r="G20" s="1">
+      <c r="H20" s="1">
         <v>20</v>
       </c>
-      <c r="H20" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="21" spans="3:8">
+      <c r="I20" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="3:9">
       <c r="C21" s="1">
         <v>16</v>
       </c>
       <c r="D21" s="1">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E21" s="1">
+        <v>9</v>
+      </c>
+      <c r="F21" s="1">
         <v>12</v>
       </c>
-      <c r="F21" s="1">
+      <c r="G21" s="1">
         <v>94</v>
       </c>
-      <c r="G21" s="1">
+      <c r="H21" s="1">
         <v>20</v>
       </c>
-      <c r="H21" s="1" t="s">
+      <c r="I21" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23" spans="3:9">
+      <c r="C23" s="1">
+        <v>17</v>
+      </c>
+      <c r="D23" s="1">
+        <v>2</v>
+      </c>
+      <c r="E23" s="1">
+        <v>6</v>
+      </c>
+      <c r="F23" s="1">
+        <v>3</v>
+      </c>
+      <c r="G23" s="1">
+        <v>93</v>
+      </c>
+      <c r="H23" s="1">
+        <v>5</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="3:9">
+      <c r="C24" s="1">
+        <v>18</v>
+      </c>
+      <c r="D24" s="1">
+        <v>2</v>
+      </c>
+      <c r="E24" s="1">
+        <v>6</v>
+      </c>
+      <c r="F24" s="1">
+        <v>6</v>
+      </c>
+      <c r="G24" s="1">
+        <v>92</v>
+      </c>
+      <c r="H24" s="1">
+        <v>5</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="3:9">
+      <c r="C25" s="1">
+        <v>19</v>
+      </c>
+      <c r="D25" s="1">
+        <v>2</v>
+      </c>
+      <c r="E25" s="1">
+        <v>6</v>
+      </c>
+      <c r="F25" s="1">
+        <v>9</v>
+      </c>
+      <c r="G25" s="1">
+        <v>91</v>
+      </c>
+      <c r="H25" s="1">
+        <v>5</v>
+      </c>
+      <c r="I25" s="1" t="s">
         <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="3:9">
+      <c r="C26" s="1">
+        <v>20</v>
+      </c>
+      <c r="D26" s="1">
+        <v>2</v>
+      </c>
+      <c r="E26" s="1">
+        <v>6</v>
+      </c>
+      <c r="F26" s="1">
+        <v>12</v>
+      </c>
+      <c r="G26" s="1">
+        <v>94</v>
+      </c>
+      <c r="H26" s="1">
+        <v>5</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="3:9">
+      <c r="C27" s="1">
+        <v>21</v>
+      </c>
+      <c r="D27" s="1">
+        <v>2</v>
+      </c>
+      <c r="E27" s="1">
+        <v>7</v>
+      </c>
+      <c r="F27" s="1">
+        <v>3</v>
+      </c>
+      <c r="G27" s="1">
+        <v>93</v>
+      </c>
+      <c r="H27" s="1">
+        <v>10</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28" spans="3:9">
+      <c r="C28" s="1">
+        <v>22</v>
+      </c>
+      <c r="D28" s="1">
+        <v>2</v>
+      </c>
+      <c r="E28" s="1">
+        <v>7</v>
+      </c>
+      <c r="F28" s="1">
+        <v>6</v>
+      </c>
+      <c r="G28" s="1">
+        <v>92</v>
+      </c>
+      <c r="H28" s="1">
+        <v>10</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="3:9">
+      <c r="C29" s="1">
+        <v>23</v>
+      </c>
+      <c r="D29" s="1">
+        <v>2</v>
+      </c>
+      <c r="E29" s="1">
+        <v>7</v>
+      </c>
+      <c r="F29" s="1">
+        <v>9</v>
+      </c>
+      <c r="G29" s="1">
+        <v>91</v>
+      </c>
+      <c r="H29" s="1">
+        <v>10</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30" spans="3:9">
+      <c r="C30" s="1">
+        <v>24</v>
+      </c>
+      <c r="D30" s="1">
+        <v>2</v>
+      </c>
+      <c r="E30" s="1">
+        <v>7</v>
+      </c>
+      <c r="F30" s="1">
+        <v>12</v>
+      </c>
+      <c r="G30" s="1">
+        <v>94</v>
+      </c>
+      <c r="H30" s="1">
+        <v>10</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31" spans="3:9">
+      <c r="C31" s="1">
+        <v>25</v>
+      </c>
+      <c r="D31" s="1">
+        <v>2</v>
+      </c>
+      <c r="E31" s="1">
+        <v>8</v>
+      </c>
+      <c r="F31" s="1">
+        <v>3</v>
+      </c>
+      <c r="G31" s="1">
+        <v>93</v>
+      </c>
+      <c r="H31" s="1">
+        <v>15</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32" spans="3:9">
+      <c r="C32" s="1">
+        <v>26</v>
+      </c>
+      <c r="D32" s="1">
+        <v>2</v>
+      </c>
+      <c r="E32" s="1">
+        <v>8</v>
+      </c>
+      <c r="F32" s="1">
+        <v>6</v>
+      </c>
+      <c r="G32" s="1">
+        <v>92</v>
+      </c>
+      <c r="H32" s="1">
+        <v>15</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33" spans="3:9">
+      <c r="C33" s="1">
+        <v>27</v>
+      </c>
+      <c r="D33" s="1">
+        <v>2</v>
+      </c>
+      <c r="E33" s="1">
+        <v>8</v>
+      </c>
+      <c r="F33" s="1">
+        <v>9</v>
+      </c>
+      <c r="G33" s="1">
+        <v>91</v>
+      </c>
+      <c r="H33" s="1">
+        <v>15</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="34" spans="3:9">
+      <c r="C34" s="1">
+        <v>28</v>
+      </c>
+      <c r="D34" s="1">
+        <v>2</v>
+      </c>
+      <c r="E34" s="1">
+        <v>8</v>
+      </c>
+      <c r="F34" s="1">
+        <v>12</v>
+      </c>
+      <c r="G34" s="1">
+        <v>94</v>
+      </c>
+      <c r="H34" s="1">
+        <v>15</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="35" spans="3:9">
+      <c r="C35" s="1">
+        <v>29</v>
+      </c>
+      <c r="D35" s="1">
+        <v>2</v>
+      </c>
+      <c r="E35" s="1">
+        <v>9</v>
+      </c>
+      <c r="F35" s="1">
+        <v>3</v>
+      </c>
+      <c r="G35" s="1">
+        <v>93</v>
+      </c>
+      <c r="H35" s="1">
+        <v>20</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="36" spans="3:9">
+      <c r="C36" s="1">
+        <v>30</v>
+      </c>
+      <c r="D36" s="1">
+        <v>2</v>
+      </c>
+      <c r="E36" s="1">
+        <v>9</v>
+      </c>
+      <c r="F36" s="1">
+        <v>6</v>
+      </c>
+      <c r="G36" s="1">
+        <v>92</v>
+      </c>
+      <c r="H36" s="1">
+        <v>20</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37" spans="3:9">
+      <c r="C37" s="1">
+        <v>31</v>
+      </c>
+      <c r="D37" s="1">
+        <v>2</v>
+      </c>
+      <c r="E37" s="1">
+        <v>9</v>
+      </c>
+      <c r="F37" s="1">
+        <v>9</v>
+      </c>
+      <c r="G37" s="1">
+        <v>91</v>
+      </c>
+      <c r="H37" s="1">
+        <v>20</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="38" spans="3:9">
+      <c r="C38" s="1">
+        <v>32</v>
+      </c>
+      <c r="D38" s="1">
+        <v>2</v>
+      </c>
+      <c r="E38" s="1">
+        <v>9</v>
+      </c>
+      <c r="F38" s="1">
+        <v>12</v>
+      </c>
+      <c r="G38" s="1">
+        <v>94</v>
+      </c>
+      <c r="H38" s="1">
+        <v>20</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:C5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="D3 D4 D5 C3:C5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/ShengxiaoGroupConfig.xlsx
+++ b/Excel/ShengxiaoGroupConfig.xlsx
@@ -1483,7 +1483,7 @@
         <v>93</v>
       </c>
       <c r="H23" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I23" s="1" t="s">
         <v>9</v>
@@ -1506,7 +1506,7 @@
         <v>92</v>
       </c>
       <c r="H24" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I24" s="1" t="s">
         <v>10</v>
@@ -1529,7 +1529,7 @@
         <v>91</v>
       </c>
       <c r="H25" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I25" s="1" t="s">
         <v>11</v>
@@ -1552,7 +1552,7 @@
         <v>94</v>
       </c>
       <c r="H26" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I26" s="1" t="s">
         <v>12</v>
@@ -1575,7 +1575,7 @@
         <v>93</v>
       </c>
       <c r="H27" s="1">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I27" s="1" t="s">
         <v>9</v>
@@ -1598,7 +1598,7 @@
         <v>92</v>
       </c>
       <c r="H28" s="1">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I28" s="1" t="s">
         <v>10</v>
@@ -1621,7 +1621,7 @@
         <v>91</v>
       </c>
       <c r="H29" s="1">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I29" s="1" t="s">
         <v>11</v>
@@ -1644,7 +1644,7 @@
         <v>94</v>
       </c>
       <c r="H30" s="1">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I30" s="1" t="s">
         <v>12</v>
@@ -1667,7 +1667,7 @@
         <v>93</v>
       </c>
       <c r="H31" s="1">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I31" s="1" t="s">
         <v>9</v>
@@ -1690,7 +1690,7 @@
         <v>92</v>
       </c>
       <c r="H32" s="1">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I32" s="1" t="s">
         <v>10</v>
@@ -1713,7 +1713,7 @@
         <v>91</v>
       </c>
       <c r="H33" s="1">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I33" s="1" t="s">
         <v>11</v>
@@ -1736,7 +1736,7 @@
         <v>94</v>
       </c>
       <c r="H34" s="1">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I34" s="1" t="s">
         <v>12</v>
@@ -1759,7 +1759,7 @@
         <v>93</v>
       </c>
       <c r="H35" s="1">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I35" s="1" t="s">
         <v>9</v>
@@ -1782,7 +1782,7 @@
         <v>92</v>
       </c>
       <c r="H36" s="1">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I36" s="1" t="s">
         <v>10</v>
@@ -1805,7 +1805,7 @@
         <v>91</v>
       </c>
       <c r="H37" s="1">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I37" s="1" t="s">
         <v>11</v>
@@ -1828,7 +1828,7 @@
         <v>94</v>
       </c>
       <c r="H38" s="1">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I38" s="1" t="s">
         <v>12</v>
@@ -1836,7 +1836,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="D3 D4 D5 C3:C5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:D5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/ShengxiaoGroupConfig.xlsx
+++ b/Excel/ShengxiaoGroupConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="13">
   <si>
     <t>#</t>
   </si>
@@ -1023,7 +1023,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:I38"/>
+  <dimension ref="C1:I55"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -1834,6 +1834,374 @@
         <v>12</v>
       </c>
     </row>
+    <row r="40" spans="3:9">
+      <c r="C40" s="1">
+        <v>33</v>
+      </c>
+      <c r="D40" s="1">
+        <v>3</v>
+      </c>
+      <c r="E40" s="1">
+        <v>6</v>
+      </c>
+      <c r="F40" s="1">
+        <v>3</v>
+      </c>
+      <c r="G40" s="1">
+        <v>93</v>
+      </c>
+      <c r="H40" s="1">
+        <v>15</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="41" spans="3:9">
+      <c r="C41" s="1">
+        <v>34</v>
+      </c>
+      <c r="D41" s="1">
+        <v>3</v>
+      </c>
+      <c r="E41" s="1">
+        <v>6</v>
+      </c>
+      <c r="F41" s="1">
+        <v>6</v>
+      </c>
+      <c r="G41" s="1">
+        <v>92</v>
+      </c>
+      <c r="H41" s="1">
+        <v>15</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42" spans="3:9">
+      <c r="C42" s="1">
+        <v>35</v>
+      </c>
+      <c r="D42" s="1">
+        <v>3</v>
+      </c>
+      <c r="E42" s="1">
+        <v>6</v>
+      </c>
+      <c r="F42" s="1">
+        <v>9</v>
+      </c>
+      <c r="G42" s="1">
+        <v>91</v>
+      </c>
+      <c r="H42" s="1">
+        <v>15</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="43" spans="3:9">
+      <c r="C43" s="1">
+        <v>36</v>
+      </c>
+      <c r="D43" s="1">
+        <v>3</v>
+      </c>
+      <c r="E43" s="1">
+        <v>6</v>
+      </c>
+      <c r="F43" s="1">
+        <v>12</v>
+      </c>
+      <c r="G43" s="1">
+        <v>94</v>
+      </c>
+      <c r="H43" s="1">
+        <v>15</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="44" spans="3:9">
+      <c r="C44" s="1">
+        <v>37</v>
+      </c>
+      <c r="D44" s="1">
+        <v>3</v>
+      </c>
+      <c r="E44" s="1">
+        <v>7</v>
+      </c>
+      <c r="F44" s="1">
+        <v>3</v>
+      </c>
+      <c r="G44" s="1">
+        <v>93</v>
+      </c>
+      <c r="H44" s="1">
+        <v>20</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="45" spans="3:9">
+      <c r="C45" s="1">
+        <v>38</v>
+      </c>
+      <c r="D45" s="1">
+        <v>3</v>
+      </c>
+      <c r="E45" s="1">
+        <v>7</v>
+      </c>
+      <c r="F45" s="1">
+        <v>6</v>
+      </c>
+      <c r="G45" s="1">
+        <v>92</v>
+      </c>
+      <c r="H45" s="1">
+        <v>20</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="46" spans="3:9">
+      <c r="C46" s="1">
+        <v>39</v>
+      </c>
+      <c r="D46" s="1">
+        <v>3</v>
+      </c>
+      <c r="E46" s="1">
+        <v>7</v>
+      </c>
+      <c r="F46" s="1">
+        <v>9</v>
+      </c>
+      <c r="G46" s="1">
+        <v>91</v>
+      </c>
+      <c r="H46" s="1">
+        <v>20</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="47" spans="3:9">
+      <c r="C47" s="1">
+        <v>40</v>
+      </c>
+      <c r="D47" s="1">
+        <v>3</v>
+      </c>
+      <c r="E47" s="1">
+        <v>7</v>
+      </c>
+      <c r="F47" s="1">
+        <v>12</v>
+      </c>
+      <c r="G47" s="1">
+        <v>94</v>
+      </c>
+      <c r="H47" s="1">
+        <v>20</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="48" spans="3:9">
+      <c r="C48" s="1">
+        <v>41</v>
+      </c>
+      <c r="D48" s="1">
+        <v>3</v>
+      </c>
+      <c r="E48" s="1">
+        <v>8</v>
+      </c>
+      <c r="F48" s="1">
+        <v>3</v>
+      </c>
+      <c r="G48" s="1">
+        <v>93</v>
+      </c>
+      <c r="H48" s="1">
+        <v>25</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="49" spans="3:9">
+      <c r="C49" s="1">
+        <v>42</v>
+      </c>
+      <c r="D49" s="1">
+        <v>3</v>
+      </c>
+      <c r="E49" s="1">
+        <v>8</v>
+      </c>
+      <c r="F49" s="1">
+        <v>6</v>
+      </c>
+      <c r="G49" s="1">
+        <v>92</v>
+      </c>
+      <c r="H49" s="1">
+        <v>25</v>
+      </c>
+      <c r="I49" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50" spans="3:9">
+      <c r="C50" s="1">
+        <v>43</v>
+      </c>
+      <c r="D50" s="1">
+        <v>3</v>
+      </c>
+      <c r="E50" s="1">
+        <v>8</v>
+      </c>
+      <c r="F50" s="1">
+        <v>9</v>
+      </c>
+      <c r="G50" s="1">
+        <v>91</v>
+      </c>
+      <c r="H50" s="1">
+        <v>25</v>
+      </c>
+      <c r="I50" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="51" spans="3:9">
+      <c r="C51" s="1">
+        <v>44</v>
+      </c>
+      <c r="D51" s="1">
+        <v>3</v>
+      </c>
+      <c r="E51" s="1">
+        <v>8</v>
+      </c>
+      <c r="F51" s="1">
+        <v>12</v>
+      </c>
+      <c r="G51" s="1">
+        <v>94</v>
+      </c>
+      <c r="H51" s="1">
+        <v>25</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="52" spans="3:9">
+      <c r="C52" s="1">
+        <v>45</v>
+      </c>
+      <c r="D52" s="1">
+        <v>3</v>
+      </c>
+      <c r="E52" s="1">
+        <v>9</v>
+      </c>
+      <c r="F52" s="1">
+        <v>3</v>
+      </c>
+      <c r="G52" s="1">
+        <v>93</v>
+      </c>
+      <c r="H52" s="1">
+        <v>30</v>
+      </c>
+      <c r="I52" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="53" spans="3:9">
+      <c r="C53" s="1">
+        <v>46</v>
+      </c>
+      <c r="D53" s="1">
+        <v>3</v>
+      </c>
+      <c r="E53" s="1">
+        <v>9</v>
+      </c>
+      <c r="F53" s="1">
+        <v>6</v>
+      </c>
+      <c r="G53" s="1">
+        <v>92</v>
+      </c>
+      <c r="H53" s="1">
+        <v>30</v>
+      </c>
+      <c r="I53" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="54" spans="3:9">
+      <c r="C54" s="1">
+        <v>47</v>
+      </c>
+      <c r="D54" s="1">
+        <v>3</v>
+      </c>
+      <c r="E54" s="1">
+        <v>9</v>
+      </c>
+      <c r="F54" s="1">
+        <v>9</v>
+      </c>
+      <c r="G54" s="1">
+        <v>91</v>
+      </c>
+      <c r="H54" s="1">
+        <v>30</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="55" spans="3:9">
+      <c r="C55" s="1">
+        <v>48</v>
+      </c>
+      <c r="D55" s="1">
+        <v>3</v>
+      </c>
+      <c r="E55" s="1">
+        <v>9</v>
+      </c>
+      <c r="F55" s="1">
+        <v>12</v>
+      </c>
+      <c r="G55" s="1">
+        <v>94</v>
+      </c>
+      <c r="H55" s="1">
+        <v>30</v>
+      </c>
+      <c r="I55" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:D5" errorStyle="warning">
